--- a/stories/arbres/ATOM-SEC.RUE.003-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Colette sort avec maman. Elles marchent dans la rue. Colette reste près de l'adulte. Elle prend la main de maman. Elle tient aussi le manteau. Main ou manteau. Le manteau est doux. La main de maman est chaude. Elles passent le marché. Colette sent les oranges. Elle reste près de l'adulte. Elle marche à côté. Maman dit : près de moi. Colette serre la main. Elles avancent ensemble. Les paniers froissent. Colette sourit.</t>
+          <t>Colette sort avec maman. Elles marchent dans la rue. Colette reste près de l'adulte. Elle prend la main de maman. Elle tient aussi le manteau. Main ou manteau. Le manteau est doux. La main de maman est chaude. Elles passent le marché. Colette sent les oranges. Elle reste près de l'adulte. Elle marche à côté. Près de moi. Colette serre la main. Elles avancent ensemble. Les paniers froissent. Colette sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Colette sort avec maman. Elles marchent dans la rue. Colette reste près de l'adulte. Elle prend la main de maman. Elle tient aussi le manteau. Main ou manteau. Le manteau est doux. La main de maman est chaude. Elles passent le marché. Colette sent les oranges. Elle reste près de l'adulte. Elle marche à côté.
+maman|Près de moi.
+narrateur|Colette serre la main. Elles avancent ensemble. Les paniers froissent. Colette sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Colette marche dans la rue. Où est-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Colette est près de maman. La main tient le manteau. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1840,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Colette garde la main de maman. Elles rentrent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2007,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.003-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Colette serre la main. Elles avancent ensemble. Les paniers froissent. Colette sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Colette marche dans la rue. Où est-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Colette est près de maman. La main tient le manteau. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1853,7 @@
           <t>narrateur|Colette garde la main de maman. Elles rentrent à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.003-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Colette près de maman</t>
+          <t>Les brioches de la ruelle</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dans la ruelle aux volets bleus, Victorina veut des brioches chaudes. Un volet claque, une bille au sol : elles restent près, prennent la bille ensemble, et le sac sent le beurre.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Colette sort avec maman. Elles marchent dans la rue. Colette reste près de l'adulte. Elle prend la main de maman. Elle tient aussi le manteau. Main ou manteau. Le manteau est doux. La main de maman est chaude. Elles passent le marché. Colette sent les oranges. Elle reste près de l'adulte. Elle marche à côté. Près de moi. Colette serre la main. Elles avancent ensemble. Les paniers froissent. Colette sourit.</t>
+          <t>Les volets bleus claquent tout doux. La peinture s'écaille un peu. La ruelle sent le linge au soleil. Un chat gris dort sur une marche. Le manteau de maman est bleu aussi. Un sac de toile pend au bras. Victorina vit ici, avec maman. Maman, les volets sont bleus ! Oui. Le four du boulanger est allumé. Tu as vu le sac chaud, hier ? Les brioches ? Oui. Je les veux. On y va ensemble ? Oui. En ce moment, Victorina prend le manteau. Le tissu est doux, un peu rêche. Main ou manteau. Près de moi. Maman ferme la porte. La ruelle est étroite, toute calme. Victorina reste près de l'adulte. Ses pieds collent à ceux de maman. Le chat ouvre un œil. Il dort encore. On le laisse. Un volet claque plus fort. Le bleu tremble au vent. Ça a fait peur ! Je suis là, tout près. Victorina serre la manche. La manche est chaude. Tes pieds sont à côté ? Oui, maman. Elles avancent entre les murs. Ça sent déjà le beurre chaud. Une bille rouge brille au sol. Une bille ! On reste près. On la prend ensemble. Maman se baisse, tout doux. Victorina se baisse aussi, collée. La bille est lisse, un peu froide. Elle est rouge. Oui. Dans le sac, avec nous. Victorina reprend la manche. Elles restent près de l'adulte. La maison aux volets bleus arrive. Le four sent le beurre, tout fort. Les brioches ! On sonne ensemble. Victorina reste collée au manteau. La cloche de la porte tinte. Un sac chaud passe dans les mains. Il est chaud ! Oui. On rentre près de moi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Colette sort avec maman. Elles marchent dans la rue. Colette reste &lt;emphasis level="moderate"&gt;près&lt;/emphasis&gt; de l'adulte. Elle prend la main de maman. Elle tient aussi le manteau. Main ou manteau. Le manteau est doux. La main de maman est chaude. Elles passent le marché. Colette sent les oranges. Elle reste près de l'adulte. Elle marche à côté. Maman dit : près de moi. Colette serre la main. Elles avancent ensemble. Les paniers froissent. Colette sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les volets bleus claquent tout doux. La peinture s'écaille un peu. La ruelle sent le linge au soleil. Un chat gris dort sur une marche. Le manteau de maman est bleu aussi. Un sac de toile pend au bras. Victorina vit ici, avec maman. Maman, les volets sont bleus ! Oui. Le four du boulanger est allumé. Tu as vu le sac chaud, hier ? Les brioches ? Oui. Je les veux. On y va ensemble ? Oui. En ce moment, Victorina prend le manteau. Le tissu est doux, un peu rêche. Main ou manteau. Près de moi. Maman ferme la porte. La ruelle est étroite, toute calme. Victorina reste près de l'adulte. Ses pieds collent à ceux de maman. Le chat ouvre un œil. Il dort encore. On le laisse. Un volet claque plus fort. Le bleu tremble au vent. Ça a fait peur ! Je suis là, tout près. Victorina serre la manche. La manche est chaude. Tes pieds sont à côté ? Oui, maman. Elles avancent entre les murs. Ça sent déjà le beurre chaud. Une bille rouge brille au sol. Une bille ! On reste près. On la prend ensemble. Maman se baisse, tout doux. Victorina se baisse aussi, collée. La bille est lisse, un peu froide. Elle est rouge. Oui. Dans le sac, avec nous. Victorina reprend la manche. Elles restent près de l'adulte. La maison aux volets bleus arrive. Le four sent le beurre, tout fort. Les brioches ! On sonne ensemble. Victorina reste collée au manteau. La cloche de la porte tinte. Un sac chaud passe dans les mains. Il est chaud ! Oui. On rentre près de moi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Colette sort avec maman. Elles marchent dans la rue. Colette reste près de l'adulte. Elle prend la main de maman. Elle tient aussi le manteau. Main ou manteau. Le manteau est doux. La main de maman est chaude. Elles passent le marché. Colette sent les oranges. Elle reste près de l'adulte. Elle marche à côté.
+          <t>narrateur|Les volets bleus claquent tout doux.
+narrateur|La peinture s'écaille un peu.
+narrateur|La ruelle sent le linge au soleil.
+narrateur|Un chat gris dort sur une marche.
+narrateur|Le manteau de maman est bleu aussi.
+narrateur|Un sac de toile pend au bras.
+narrateur|Victorina vit ici, avec maman.
+enfant-f|Maman, les volets sont bleus !
+maman|Oui.
+maman|Le four du boulanger est allumé.
+maman|Tu as vu le sac chaud, hier ?
+enfant-f|Les brioches ?
+maman|Oui.
+enfant-f|Je les veux.
+maman|On y va ensemble ?
+enfant-f|Oui.
+narrateur|En ce moment, Victorina prend le manteau.
+narrateur|Le tissu est doux, un peu rêche.
+maman|Main ou manteau.
 maman|Près de moi.
-narrateur|Colette serre la main. Elles avancent ensemble. Les paniers froissent. Colette sourit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Maman ferme la porte.
+narrateur|La ruelle est étroite, toute calme.
+narrateur|Victorina reste près de l'adulte.
+narrateur|Ses pieds collent à ceux de maman.
+narrateur|Le chat ouvre un œil.
+enfant-f|Il dort encore.
+maman|On le laisse.
+narrateur|Un volet claque plus fort.
+narrateur|Le bleu tremble au vent.
+enfant-f|Ça a fait peur !
+maman|Je suis là, tout près.
+narrateur|Victorina serre la manche.
+narrateur|La manche est chaude.
+maman|Tes pieds sont à côté ?
+enfant-f|Oui, maman.
+narrateur|Elles avancent entre les murs.
+narrateur|Ça sent déjà le beurre chaud.
+narrateur|Une bille rouge brille au sol.
+enfant-f|Une bille !
+maman|On reste près.
+maman|On la prend ensemble.
+narrateur|Maman se baisse, tout doux.
+narrateur|Victorina se baisse aussi, collée.
+narrateur|La bille est lisse, un peu froide.
+enfant-f|Elle est rouge.
+maman|Oui.
+maman|Dans le sac, avec nous.
+narrateur|Victorina reprend la manche.
+narrateur|Elles restent près de l'adulte.
+narrateur|La maison aux volets bleus arrive.
+narrateur|Le four sent le beurre, tout fort.
+enfant-f|Les brioches !
+maman|On sonne ensemble.
+narrateur|Victorina reste collée au manteau.
+narrateur|La cloche de la porte tinte.
+narrateur|Un sac chaud passe dans les mains.
+enfant-f|Il est chaud !
+maman|Oui.
+maman|On rentre près de moi.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,12 +1409,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Colette marche dans la rue. Où est-elle ?</t>
+          <t>Victorina marche dans la ruelle. Où est-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Colette marche dans la rue. Où est-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina marche dans la ruelle. Où est-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1377,7 +1444,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle reste près. Elle tient la main. Où est Colette ?</t>
+          <t>Elle reste près. Elle tient le manteau. Où est Victorina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1426,7 +1493,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1569,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Colette marche dans la rue. Où est-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorina marche dans la ruelle.
+narrateur|Où est-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1597,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Colette est près de maman. La main tient le manteau. Maman est là.</t>
+          <t>Victorina est près de maman. La main tient le manteau bleu. Les pieds restent à côté. Tu es près de moi ? Oui, maman. Main ou manteau. Bravo, Victorina. Le sac de toile est tout tiède. Ça sent le beurre et le sucre. La bille rouge roule dans le sac. Elle fait du bruit. Oui. On rentre ensemble. Le chat est encore sur la marche. Victorina le regarde, tout près. Elle garde la manche. Tu tiens bien le manteau ? Oui. Un autre volet claque, plus loin. Victorina serre plus fort. Près de moi. Elles passent le chat, tout doux. La porte de la maison arrive.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Colette est &lt;emphasis level="moderate"&gt;près&lt;/emphasis&gt; de maman. La main tient le manteau. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina est près de maman. La main tient le manteau bleu. Les pieds restent à côté. Tu es près de moi ? Oui, maman. Main ou manteau. Bravo, Victorina. Le sac de toile est tout tiède. Ça sent le beurre et le sucre. La bille rouge roule dans le sac. Elle fait du bruit. Oui. On rentre ensemble. Le chat est encore sur la marche. Victorina le regarde, tout près. Elle garde la manche. Tu tiens bien le manteau ? Oui. Un autre volet claque, plus loin. Victorina serre plus fort. Près de moi. Elles passent le chat, tout doux. La porte de la maison arrive.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1591,14 +1658,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,10 +1745,31 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Colette est près de maman. La main tient le manteau. Maman est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorina est près de maman.
+narrateur|La main tient le manteau bleu.
+narrateur|Les pieds restent à côté.
+maman|Tu es près de moi ?
+enfant-f|Oui, maman.
+enfant-f|Main ou manteau.
+maman|Bravo, Victorina.
+narrateur|Le sac de toile est tout tiède.
+narrateur|Ça sent le beurre et le sucre.
+narrateur|La bille rouge roule dans le sac.
+enfant-f|Elle fait du bruit.
+maman|Oui.
+maman|On rentre ensemble.
+narrateur|Le chat est encore sur la marche.
+narrateur|Victorina le regarde, tout près.
+narrateur|Elle garde la manche.
+maman|Tu tiens bien le manteau ?
+enfant-f|Oui.
+narrateur|Un autre volet claque, plus loin.
+narrateur|Victorina serre plus fort.
+maman|Près de moi.
+narrateur|Elles passent le chat, tout doux.
+narrateur|La porte de la maison arrive.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,12 +1794,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Colette garde la main de maman. Elles rentrent à la maison.</t>
+          <t>Maman ouvre la porte. L'air de la maison est tiède. Tu poses le sac ? Oui. Victorina pose le sac sur la table. Le papier craque, tout chaud. Deux brioches sentent le beurre. Elles sont dorées ! Oui. Merci d'avoir tenu le manteau. La bille rouge sort du sac. Elle brille près du pain. On l'a prise ensemble. Oui. Dans la ruelle, près de moi. Le manteau bleu sèche un peu. La peinture des volets reste dehors.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Colette garde la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Elles rentrent à la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman ouvre la porte. L'air de la maison est tiède. Tu poses le sac ? Oui. Victorina pose le sac sur la table. Le papier craque, tout chaud. Deux brioches sentent le beurre. Elles sont dorées ! Oui. Merci d'avoir tenu le manteau. La bille rouge sort du sac. Elle brille près du pain. On l'a prise ensemble. Oui. Dans la ruelle, près de moi. Le manteau bleu sèche un peu. La peinture des volets reste dehors.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,14 +1855,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1850,10 +1938,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Colette garde la main de maman. Elles rentrent à la maison.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman ouvre la porte.
+narrateur|L'air de la maison est tiède.
+maman|Tu poses le sac ?
+enfant-f|Oui.
+narrateur|Victorina pose le sac sur la table.
+narrateur|Le papier craque, tout chaud.
+narrateur|Deux brioches sentent le beurre.
+enfant-f|Elles sont dorées !
+maman|Oui.
+maman|Merci d'avoir tenu le manteau.
+narrateur|La bille rouge sort du sac.
+narrateur|Elle brille près du pain.
+enfant-f|On l'a prise ensemble.
+maman|Oui.
+maman|Dans la ruelle, près de moi.
+narrateur|Le manteau bleu sèche un peu.
+narrateur|La peinture des volets reste dehors.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,12 +1981,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai tenu le manteau. Les brioches sont chaudes. Bravo, Victorina. Le beurre sent encore le sac. Une brioche chauffe sa main.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai tenu le manteau. Les brioches sont chaudes. Bravo, Victorina. Le beurre sent encore le sac. Une brioche chauffe sa main.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,14 +2042,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2121,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|J'ai tenu le manteau.
+enfant-f|Les brioches sont chaudes.
+maman|Bravo, Victorina.
+narrateur|Le beurre sent encore le sac.
+narrateur|Une brioche chauffe sa main.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2184,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.003-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-08.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rue du marché</t>
+          <t>ruelle aux volets bleus, chat sur la marche, four du boulanger</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Colette, maman</t>
+          <t>Victorina, maman</t>
         </is>
       </c>
     </row>
